--- a/docs/spec/2026-07-02-behavioral-spec.xlsx
+++ b/docs/spec/2026-07-02-behavioral-spec.xlsx
@@ -458,10 +458,10 @@
         <v>As a staff user I want to log in with email+password so I can reach the internal app</v>
       </c>
       <c r="D2" t="str">
-        <v>Login.tsx form calls useAuth.signIn -&gt; supabase.auth.signInWithPassword on the internal client; useAuth loads the user_profiles row and exposes profile/capabilities; a missing or inactive profile keeps the user out of protected routes; success lands on /painel via ProtectedRoute redirect logic; errors shown inline.</v>
+        <v>Login.tsx form calls useAuth.signIn -&gt; supabase.auth.signInWithPassword on the internal client; useAuth loads the user_profiles row and exposes profile/capabilities; a missing or inactive profile keeps the user out of protected routes; on success Login.tsx navigates to /painel itself (an already-authenticated visitor is redirected by a Navigate guard); errors shown inline.</v>
       </c>
       <c r="E2" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F2" t="str">
         <v>-</v>
@@ -476,7 +476,7 @@
         <v>src/pages/Login.tsx; src/hooks/useAuth.tsx; src/services/supabase.ts</v>
       </c>
       <c r="J2" t="str">
-        <v>-</v>
+        <v>Verified by code read — SQL/trigger/cron/edge or live-DB RLS surface with no executable assertion in this environment (static is the strongest method available).</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>Route mounted under ProtectedRoute adminOnly; AdminUsuarios.tsx lists user_profiles, toggles role/active via src/services/adminUsers.ts, and shows audit-log and metrics tabs with dedicated loading/error states; mutations invalidate users/audit/metrics queries.</v>
       </c>
       <c r="E3" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F3" t="str">
         <v>-</v>
@@ -525,7 +525,7 @@
         <v>adminUsers.ts updates user_profiles and writes audit_logs rows with changed_by=auth.uid(); observability queries aggregate audit logs and login metrics for the admin screen.</v>
       </c>
       <c r="E4" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F4" t="str">
         <v>-</v>
@@ -557,7 +557,7 @@
         <v>src/services/supabase.ts creates two clients: supabase (staff) and supabasePortal with its own storageKey ('td-portal-auth') and detectSessionInUrl:false; the sessions coexist and logging out of one does not drop the other.</v>
       </c>
       <c r="E5" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F5" t="str">
         <v>-</v>
@@ -566,13 +566,13 @@
         <v>-</v>
       </c>
       <c r="H5" t="str">
-        <v>Vitest: supabaseAuth.test.ts</v>
+        <v>Static</v>
       </c>
       <c r="I5" t="str">
         <v>src/services/supabase.ts; src/services/supabaseAuth.ts</v>
       </c>
       <c r="J5" t="str">
-        <v>-</v>
+        <v>supabaseAuth.test.ts only exercises signOut; the storageKey/detectSessionInUrl isolation is verified statically.</v>
       </c>
     </row>
     <row r="6">
@@ -589,7 +589,7 @@
         <v>ProtectedRoute (staff), ProtectedRoute adminOnly (admin screens) and PortalProtectedRoute (portal) gate navigation in src/App.tsx; per ADR 0004 these are UX barriers only — authorization is enforced by RLS policies, grants and RPC guards in Postgres.</v>
       </c>
       <c r="E6" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F6" t="str">
         <v>-</v>
@@ -621,7 +621,7 @@
         <v>RLS (010_rls_by_role.sql + later fixes): self/admin SELECT; a user updates only their own row and only while active; INSERT/DELETE admin-only. Helpers is_active_user()/is_admin()/current_user_role() underpin all role-based policies.</v>
       </c>
       <c r="E7" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F7" t="str">
         <v>-</v>
@@ -636,7 +636,7 @@
         <v>supabase/migrations/010_rls_by_role.sql; supabase/migrations/077_fix_user_profile_privilege_escalation.sql</v>
       </c>
       <c r="J7" t="str">
-        <v>-</v>
+        <v>Verified by code read — SQL/trigger/cron/edge or live-DB RLS surface with no executable assertion in this environment (static is the strongest method available).</v>
       </c>
     </row>
     <row r="8">
@@ -653,7 +653,7 @@
         <v>prevent_user_profile_privilege_escalation() BEFORE UPDATE on user_profiles rejects a user changing their own role or active flag; service_role remains allowed for provisioning.</v>
       </c>
       <c r="E8" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F8" t="str">
         <v>-</v>
@@ -668,7 +668,7 @@
         <v>supabase/migrations/077_fix_user_profile_privilege_escalation.sql</v>
       </c>
       <c r="J8" t="str">
-        <v>-</v>
+        <v>Verified by code read — SQL/trigger/cron/edge or live-DB RLS surface with no executable assertion in this environment (static is the strongest method available).</v>
       </c>
     </row>
     <row r="9">
@@ -685,7 +685,7 @@
         <v>ADR 0011 default-deny: migrations revoke EXECUTE from PUBLIC/anon on all public SECURITY DEFINER functions; 150_revoke_anon_portal_read_rpcs.sql removes the anon grants that six portal read RPCs had regained; 152_revoke_anon_definer_drift.sql re-runs the comprehensive revoke carving out only portal_resolve_login(text) (ADR 0013); 151_guard_definer_rpcs_active_user.sql adds is_active_user() guards to definer readers that lacked them.</v>
       </c>
       <c r="E9" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F9" t="str">
         <v>-</v>
@@ -717,7 +717,7 @@
         <v>Painel.tsx queries bls/containers/voyages/invoices and composes KPI cards plus the Line-Up snapshot from src/services/lineup.ts; caches ['dashboard'] and ['lineup-tv-v3']; distinct-container counting is done client-side by the containerCounts helper.</v>
       </c>
       <c r="E10" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F10" t="str">
         <v>-</v>
@@ -749,7 +749,7 @@
         <v>Alertas.tsx via useOperationalAlerts/src/services/alerts.ts reads the alerts table, transitions status (open -&gt; acknowledged -&gt; closed) and invalidates alerts, op-count and dashboard caches.</v>
       </c>
       <c r="E11" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F11" t="str">
         <v>-</v>
@@ -781,7 +781,7 @@
         <v>Relatorios.tsx composes operational/financial/per-customer/demurrage tabs reading B/Ls, invoices, customers and demurrage via src/services/reports.ts; exports generate local XLSX files via src/services/exports.ts (lazy @e965/xlsx import).</v>
       </c>
       <c r="E12" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F12" t="str">
         <v>-</v>
@@ -813,7 +813,7 @@
         <v>LineUpTV.tsx renders Navigate to /painel with replace so no extra history entry is created.</v>
       </c>
       <c r="E13" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F13" t="str">
         <v>-</v>
@@ -845,7 +845,7 @@
         <v>LineUpTVDisplay.tsx renders outside AppLayout, loads fetchLineUpSnapshot into cache ['lineup-tv-display-v2'], rotates pages on a timer and offers fullscreen; it sits inside the authenticated route group.</v>
       </c>
       <c r="E14" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F14" t="str">
         <v>-</v>
@@ -877,7 +877,7 @@
         <v>The catch-all route in src/App.tsx renders Navigate to /painel with replace; the destination then applies the normal auth guards.</v>
       </c>
       <c r="E15" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F15" t="str">
         <v>-</v>
@@ -892,7 +892,7 @@
         <v>src/App.tsx</v>
       </c>
       <c r="J15" t="str">
-        <v>-</v>
+        <v>Verified by code read — SQL/trigger/cron/edge or live-DB RLS surface with no executable assertion in this environment (static is the strongest method available).</v>
       </c>
     </row>
     <row r="16">
@@ -909,7 +909,7 @@
         <v>count_distinct_containers() -&gt; bigint (045_count_distinct_containers_fn.sql), STABLE SECURITY INVOKER, PUBLIC revoked, authenticated granted; read-only aggregate. No frontend caller exists in src today.</v>
       </c>
       <c r="E16" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F16" t="str">
         <v>-</v>
@@ -941,7 +941,7 @@
         <v>010_rls_by_role.sql: active users read/insert/update alerts; only admin deletes; alert writers include overdue detection and portal dispute flows.</v>
       </c>
       <c r="E17" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F17" t="str">
         <v>-</v>
@@ -956,7 +956,7 @@
         <v>supabase/migrations/010_rls_by_role.sql; src/services/alerts.ts</v>
       </c>
       <c r="J17" t="str">
-        <v>-</v>
+        <v>Verified by code read — SQL/trigger/cron/edge or live-DB RLS surface with no executable assertion in this environment (static is the strongest method available).</v>
       </c>
     </row>
     <row r="18">
@@ -973,7 +973,7 @@
         <v>014_lock_down_financial_reads_and_audit_writes.sql: active users read; INSERT requires active profile and changed_by=auth.uid(); UPDATE/DELETE admin-only. audit_logs feeds B/L timeline, voyage timeline and admin observability.</v>
       </c>
       <c r="E18" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F18" t="str">
         <v>-</v>
@@ -988,7 +988,7 @@
         <v>supabase/migrations/014_lock_down_financial_reads_and_audit_writes.sql</v>
       </c>
       <c r="J18" t="str">
-        <v>-</v>
+        <v>Verified by code read — SQL/trigger/cron/edge or live-DB RLS surface with no executable assertion in this environment (static is the strongest method available).</v>
       </c>
     </row>
     <row r="19">
@@ -1005,7 +1005,7 @@
         <v>pg_cron job cleanup-portal-sessions (03:00 UTC, 041_rls_missing_tables.sql) deletes legacy portal sessions expired for more than one day.</v>
       </c>
       <c r="E19" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F19" t="str">
         <v>-</v>
@@ -1037,7 +1037,7 @@
         <v>pg_cron job cleanup-provision-rate-limit (03:30 UTC, 053_security_hardening.sql) removes provision-portal-user rate-limit rows older than 2 days.</v>
       </c>
       <c r="E20" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F20" t="str">
         <v>-</v>
@@ -1069,7 +1069,7 @@
         <v>Viagens.tsx loads up to 500 voyages via useVoyages plus B/Ls, batches, granito and vazios stats; VoyageFilters filters by vessel/voyage/carrier/port, period, status and reconciliation state; viagensFilters.ts sorts by next ETA; VoyageRail selection navigates to /viagens/:voyageId; rail collapse persisted in localStorage['viagens:rail-collapsed']; admins see Nova Viagem and edit.</v>
       </c>
       <c r="E21" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F21" t="str">
         <v>-</v>
@@ -1101,7 +1101,7 @@
         <v>Same Viagens.tsx page renders the detail pane for the URL voyage (ADR 0012): overview/import/export/schedules-manifests tabs, POL/POD planning cards, Mercante fields (Número de Escala, CE Master), timeline and Baplie reconciliation entry points; invalid ids fall back to the empty-selection state.</v>
       </c>
       <c r="E22" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F22" t="str">
         <v>-</v>
@@ -1133,7 +1133,7 @@
         <v>Schedule edits via voyageRouteSchedules.ts write audit_logs entries (POD/POL events); the trg_voyage_schedule_snapshot trigger then updates the voyages JSONB snapshots; mutations invalidate voyage caches and Line-Up.</v>
       </c>
       <c r="E23" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F23" t="str">
         <v>-</v>
@@ -1165,7 +1165,7 @@
         <v>voyageExportSchedules.ts upserts/deletes voyage_export_schedules rows feeding the voyage detail and Line-Up; mutations invalidate voyage/TV caches.</v>
       </c>
       <c r="E24" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F24" t="str">
         <v>-</v>
@@ -1197,7 +1197,7 @@
         <v>voyageTimeline.ts aggregates audit_logs and baplie_reconciliation_resolutions into a humanized voyage timeline with actor names from user_profiles.</v>
       </c>
       <c r="E25" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F25" t="str">
         <v>-</v>
@@ -1229,7 +1229,7 @@
         <v>voyages.ts pre-checks dependencies (B/Ls, manifests, granito, vazios, vehicles) before allowing delete; RLS keeps DELETE admin-only; audited via audit_logs.</v>
       </c>
       <c r="E26" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F26" t="str">
         <v>-</v>
@@ -1261,7 +1261,7 @@
         <v>VoyageCombobox (ADR 0018) provides typeahead over vessel/voyage via useVoyageOptions: 'required' mode for imports (mandatory single voyage, no empty option) and 'clearable' mode for list filters (empty = all voyages); context screens pre-seed via initialValue but remain editable.</v>
       </c>
       <c r="E27" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F27" t="str">
         <v>-</v>
@@ -1293,7 +1293,7 @@
         <v>set_import_batch_ce_master (145_set_import_batch_ce_master_atomic.sql) updates import_batches.ce_master and audit atomically; caller in voyages.ts invalidates voyage/manifest caches.</v>
       </c>
       <c r="E28" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F28" t="str">
         <v>-</v>
@@ -1325,7 +1325,7 @@
         <v>trg_voyage_schedule_snapshot AFTER INSERT on audit_logs (POD/POL events) updates voyages JSONB snapshot; 052 fixed JSON null handling so a null new_value does not violate NOT NULL.</v>
       </c>
       <c r="E29" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F29" t="str">
         <v>-</v>
@@ -1340,7 +1340,7 @@
         <v>supabase/migrations/046_voyage_schedule_snapshot_trigger.sql; supabase/migrations/052_fix_voyage_snapshot_null_new_value.sql</v>
       </c>
       <c r="J29" t="str">
-        <v>-</v>
+        <v>Verified by code read — SQL/trigger/cron/edge or live-DB RLS surface with no executable assertion in this environment (static is the strongest method available).</v>
       </c>
     </row>
     <row r="30">
@@ -1357,7 +1357,7 @@
         <v>Final state of 010 (+ rls hardening for export schedules): active users read/insert/update; only admin deletes; voyage POD/POL snapshots maintained by trigger.</v>
       </c>
       <c r="E30" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F30" t="str">
         <v>-</v>
@@ -1389,7 +1389,7 @@
         <v>ChegadasSaidas.tsx CRUDs vessel_schedules (page-level Supabase access + vesselSchedules.ts), imports/exports XLSX, reorders lines, ends a vessel into ended_vessels and links MarineTraffic by IMO; Realtime invalidation also refreshes the Portal ShipScheduleWidget cache.</v>
       </c>
       <c r="E31" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F31" t="str">
         <v>-</v>
@@ -1421,7 +1421,7 @@
         <v>reorder_vessel_schedules (135_atomic_vessel_schedule_operations.sql) persists a new display order in one call; requires active user; caller invalidates schedule caches.</v>
       </c>
       <c r="E32" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F32" t="str">
         <v>-</v>
@@ -1453,7 +1453,7 @@
         <v>archive_vessel_schedule (135) snapshots the line into ended_vessels and removes it from vessel_schedules atomically; requires active user.</v>
       </c>
       <c r="E33" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F33" t="str">
         <v>-</v>
@@ -1485,7 +1485,7 @@
         <v>124_vessel_schedules.sql (+ 139 grants): SELECT for any authenticated (portal-compatible by design); INSERT/UPDATE require active internal user; DELETE admin. ended_vessels: SELECT authenticated; INSERT active; DELETE admin; no UPDATE policy exists.</v>
       </c>
       <c r="E34" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F34" t="str">
         <v>-</v>
@@ -1517,7 +1517,7 @@
         <v>Manifestos.tsx lists CNTR B/Ls with pagination, bulk selection, summary cards and filters (text, voyage, POL, POD, review, financial, charges, cargo profile); rows link to /manifestos/:blId; hosts the CNTR manifest modal, the CE Mercante modal and the Importar B/L modal; admin-only bulk delete after fiscal pre-check.</v>
       </c>
       <c r="E35" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F35" t="str">
         <v>-</v>
@@ -1549,7 +1549,7 @@
         <v>import_manifest_with_postprocess_transactional (final def in 129_review_gate_hardening.sql; billing step decoupled by 149_remove_billing_from_import_function.sql) imports batch/B/Ls/containers, POL/POD schedules, contacts and the canonical review gate in one transaction; the core import_manifest_transactional rejects duplicate (voyage_id, cargo_mode, file_hash) with 23505 and rate-limits with P0429 (frontend retries once after waiting); SHA-256 computed client-side in manifestImport.ts.</v>
       </c>
       <c r="E36" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F36" t="str">
         <v>-</v>
@@ -1581,7 +1581,7 @@
         <v>import_bl_freight_transactional(jsonb, uuid) -&gt; jsonb (162_bl_freight_lines.sql; SECURITY DEFINER; active user; p_changed_by=auth.uid(); PUBLIC/anon revoked): upserts commercial fields, bl_emission_date and bl_freight_lines; preserves omitted fields; audits every change; writes no billing data; blocks physical changes (weight/containers) when charge_calculations or invoice_bls exist unless the operator override flags are set.</v>
       </c>
       <c r="E37" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F37" t="str">
         <v>-</v>
@@ -1613,7 +1613,7 @@
         <v>BlImportModal + blParser.ts: operator must declare vessel+voyage via VoyageCombobox (required mode); the parser reads vessel/voyage from the file (A18) and blocks any row diverging from the declared voyage; POL/POD/destination normalized to UN/LOCODE; consignee document/name links the customer; billing-impact changes (container count, shared container, IMO/OOG, breakbulk weight, billed CNPJ) are shown in the preview and applied only with explicit override (audited FATURAMENTO_SOBRESCRITO), otherwise logged as ALTERACAO_OPERACIONAL_BLOQUEADA while other fields still apply (ADR 0017).</v>
       </c>
       <c r="E38" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F38" t="str">
         <v>-</v>
@@ -1645,7 +1645,7 @@
         <v>apply_ce_mercante_update(text,text,uuid) -&gt; text (012_transactional_rpcs.sql; SECURITY INVOKER; caller RLS): updates bls.ce_mercante and audits; returns 'unchanged' when the value is identical.</v>
       </c>
       <c r="E39" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F39" t="str">
         <v>-</v>
@@ -1677,7 +1677,7 @@
         <v>apply_ce_mercante_manifest(jsonb,uuid) -&gt; jsonb (087_apply_ce_mercante_manifest.sql; SECURITY INVOKER): batch-updates bls.ce_mercante with audit; caller invalidates B/L list and detail; single-manifest EDI enforced by parser.</v>
       </c>
       <c r="E40" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F40" t="str">
         <v>-</v>
@@ -1709,7 +1709,7 @@
         <v>mercanteEdiGenerator.ts renders the Mercante EDI; C5 records carry the maritime freight (offset 1739) and the expense block (3796) from bl_freight_lines with literal values and prepaid/collect indicator; bl_emission_date feeds the record; download handled by mercanteEdiDownload.</v>
       </c>
       <c r="E41" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F41" t="str">
         <v>-</v>
@@ -1741,7 +1741,7 @@
         <v>BlDetalhe.tsx tabs: Detalhes (useBlEditForm -&gt; save_bl_review with optimistic lock), Faturamento (client/charges/demurrage/invoice sections), Histórico (bl_timeline pages of 50; Auditoria = justified subset); the Importar B/L modal here is scoped to the open B/L; edits invalidate detail/list/voyage caches.</v>
       </c>
       <c r="E42" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F42" t="str">
         <v>-</v>
@@ -1773,7 +1773,7 @@
         <v>bl_timeline(p_bl_id text, p_limit int=50, p_offset int=0) -&gt; table (130_bl_timeline_rpc.sql; STABLE SECURITY DEFINER; is_active_user(); PUBLIC/anon revoked): read-only union of bl, bl_container, charge_calculation, invoice (via invoice_bls) and system events for the B/L; excludes global events.</v>
       </c>
       <c r="E43" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F43" t="str">
         <v>-</v>
@@ -1805,7 +1805,7 @@
         <v>CargaSolta.tsx previews and imports BB manifests via import_breakbulk_manifest_transactional (144_import_breakbulk_manifest_transactional.sql; atomic): rejects duplicate file/incompatible cargo mode, creates batch/B/Ls/bl_breakbulk_items and applies the batch review gate; import errors recorded per line in import_errors.</v>
       </c>
       <c r="E44" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F44" t="str">
         <v>-</v>
@@ -1837,7 +1837,7 @@
         <v>validate_bl_breakbulk_item_parent() BEFORE INSERT/UPDATE on bl_breakbulk_items (006_breakbulk_module.sql) rejects items whose parent B/L cargo mode is not carga_solta.</v>
       </c>
       <c r="E45" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F45" t="str">
         <v>-</v>
@@ -1852,7 +1852,7 @@
         <v>supabase/migrations/006_breakbulk_module.sql</v>
       </c>
       <c r="J45" t="str">
-        <v>-</v>
+        <v>Verified by code read — SQL/trigger/cron/edge or live-DB RLS surface with no executable assertion in this environment (static is the strongest method available).</v>
       </c>
     </row>
     <row r="46">
@@ -1869,7 +1869,7 @@
         <v>Containers.tsx filters bl_containers; containerDatesImport.ts imports operational dates (audited; ATA propagation per 138_audit_container_dates_and_propagate_ata.sql) and containerFlagsImport.ts imports IMO/OOG/status flags with audit; date changes feed demurrage; container delete is blocked by dependency checks in containers.ts.</v>
       </c>
       <c r="E46" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F46" t="str">
         <v>-</v>
@@ -1901,7 +1901,7 @@
         <v>Veiculos.tsx imports vehicle spreadsheets via import_vehicle_rows_transactional(jsonb) (final ACL in 109_fix_anon_executable_import_rpcs.sql; active user; atomic); relationships validated by trigger; controlled delete recalculates charges and may call cancel_invoice to release an exempt B/L.</v>
       </c>
       <c r="E47" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F47" t="str">
         <v>-</v>
@@ -1933,7 +1933,7 @@
         <v>validate_vehicle_relationships() BEFORE INSERT/UPDATE on vehicles (004_vehicles.sql; search_path fixed later) normalizes fields and rejects incoherent voyage/B/L/container combinations.</v>
       </c>
       <c r="E48" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F48" t="str">
         <v>-</v>
@@ -1948,7 +1948,7 @@
         <v>supabase/migrations/004_vehicles.sql</v>
       </c>
       <c r="J48" t="str">
-        <v>-</v>
+        <v>Verified by code read — SQL/trigger/cron/edge or live-DB RLS surface with no executable assertion in this environment (static is the strongest method available).</v>
       </c>
     </row>
     <row r="49">
@@ -1965,7 +1965,7 @@
         <v>Baplie.tsx imports EDI into per-voyage staging via import_baplie_staging_transactional(bigint,jsonb) (109; DEFINER; active+admin; atomically replaces the voyage staging); baplieReconciliation.ts compares container_number+voyage_id: existence divergences are warnings, attribute divergences (IMO/OOG/status) are operator-resolved and persisted in baplie_reconciliation_resolutions; commercial fields never overwritten by Baplie.</v>
       </c>
       <c r="E49" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F49" t="str">
         <v>-</v>
@@ -1997,7 +1997,7 @@
         <v>delete_baplie_manifest_for_voyage(bigint) -&gt; integer (097_vazios_importacao_delete_admin_only.sql; SECURITY DEFINER; search_path=''; is_active_user()): deletes only the source='baplie' manifest of the voyage; containers fall by cascade; used by the vazios reimport flow.</v>
       </c>
       <c r="E50" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F50" t="str">
         <v>-</v>
@@ -2029,7 +2029,7 @@
         <v>VaziosImportacao.tsx imports via import_vazios_importacao_transactional and replace_vazios_from_baplie_transactional (146_import_vazios_transactional.sql; atomic; active user); reimport respects manifest/source; per-voyage manifest removal available; stats via useVaziosImportacaoStats.</v>
       </c>
       <c r="E51" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F51" t="str">
         <v>-</v>
@@ -2061,7 +2061,7 @@
         <v>EmbarqueVazios.tsx imports bookings via import_vazios_bookings_transactional (146; atomic; active user); import bounded per file and voyage; filters over vazios_bookings.</v>
       </c>
       <c r="E52" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F52" t="str">
         <v>-</v>
@@ -2093,7 +2093,7 @@
         <v>src/App.tsx renders Navigate to /embarquevazios with replace.</v>
       </c>
       <c r="E53" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F53" t="str">
         <v>-</v>
@@ -2125,7 +2125,7 @@
         <v>bls.ts delete flow pre-checks invoices, invoice links, receivables and issued demurrage; blocked items are reported while deletable ones proceed bottom-up; deletions audited best-effort via deleteAudit.ts (ADR 0009).</v>
       </c>
       <c r="E54" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F54" t="str">
         <v>-</v>
@@ -2157,7 +2157,7 @@
         <v>importCore.ts / uploadLimits enforce the max file size before reading buffers or calling XLSX.read, for all untrusted import files (ADR 0005 rule).</v>
       </c>
       <c r="E55" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F55" t="str">
         <v>-</v>
@@ -2189,7 +2189,7 @@
         <v>Final state of 010: bls, bl_containers, bl_breakbulk_items — active users read/insert/update; admin deletes. bls carries review gate, promotion and billing guards via triggers; bl_containers delete additionally blocked by service-level dependency checks.</v>
       </c>
       <c r="E56" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F56" t="str">
         <v>-</v>
@@ -2204,7 +2204,7 @@
         <v>supabase/migrations/010_rls_by_role.sql</v>
       </c>
       <c r="J56" t="str">
-        <v>-</v>
+        <v>Verified by code read — SQL/trigger/cron/edge or live-DB RLS surface with no executable assertion in this environment (static is the strongest method available).</v>
       </c>
     </row>
     <row r="57">
@@ -2221,7 +2221,7 @@
         <v>162_bl_freight_lines.sql: active users read/insert/update; admin deletes; the importer writes through the transactional RPC; lines cascade with the B/L; source of Frete &amp; Despesas for preview and Mercante EDI C5.</v>
       </c>
       <c r="E57" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F57" t="str">
         <v>-</v>
@@ -2253,7 +2253,7 @@
         <v>Baplie staging/resolutions (rls hardening): active read/insert/update; admin delete. import_batches/import_errors (010): active read/insert/update; admin delete. vazios_* tables (042 + later fix removing stale permissive policies): active read/insert/update; admin delete. vehicles (010): active r/i/u; admin delete.</v>
       </c>
       <c r="E58" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F58" t="str">
         <v>-</v>
@@ -2285,7 +2285,7 @@
         <v>TaxasLocais.tsx requires UI capabilities charge_tables/charge_overrides (useAuth); CRUD via chargeTableService.ts and chargeRateService.ts over charge_tables/charge_table_items/customer_rate_overrides (all admin-only at RLS); mutations invalidate queryKeys.charges.* families; table validity gates ready_for_billing.</v>
       </c>
       <c r="E59" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F59" t="str">
         <v>-</v>
@@ -2317,7 +2317,7 @@
         <v>Revisao.tsx via useReview/review.ts shows the queue of bls+granite_bls pendencies grouped by customer (CNPJ); inline editors fix link/email/portal provisioning in batch; corrections go through save_bl_review which recomputes the canonical gate; when the canonical pendency list is empty, reviewBillingAutomation.ts attempts calculate_bl_local_charges + mark_bl_ready_and_create_invoice.</v>
       </c>
       <c r="E60" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F60" t="str">
         <v>-</v>
@@ -2349,7 +2349,7 @@
         <v>save_bl_review(text,timestamptz,jsonb,jsonb,uuid) -&gt; jsonb (final def 129_review_gate_hardening.sql; SECURITY DEFINER; active user; p_changed_by=auth.uid()): PT409 on stale timestamp; updates fields; recomputes pendencies from real state via compute_bl_review_pendencies (customer linked, contact email, portal active with auth_user_id, BB weight; CE Mercante is NOT a lock); is the only author of review_status; discards client-sent status audit and records effective before/after; syncs reconciliation queue.</v>
       </c>
       <c r="E61" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F61" t="str">
         <v>-</v>
@@ -2381,7 +2381,7 @@
         <v>calculate_bl_local_charges(text,uuid,boolean) -&gt; jsonb (098_fix_recalc_clears_billing_hold_reason.sql; guard added by 151_guard_definer_rpcs_active_user.sql): recreates automatic lines from the current table/override, updates charge status and clears billing hold; requires active user.</v>
       </c>
       <c r="E62" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F62" t="str">
         <v>-</v>
@@ -2413,7 +2413,7 @@
         <v>add_manual_bl_charge, update_manual_bl_charge and delete_manual_bl_charge (108_guard_manual_charges_and_clear_pix_on_reversal.sql; DEFINER; active user): only manual eligible lines are mutable; all audited; any mutation is blocked when the B/L is protected by an active invoice.</v>
       </c>
       <c r="E63" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F63" t="str">
         <v>-</v>
@@ -2445,7 +2445,7 @@
         <v>list_bl_local_charge_lines(text) (016) and list_manual_charge_items_for_bl(text) (019), both SECURITY DEFINER readers; 151 added the is_active_user() guard they lacked; read-only.</v>
       </c>
       <c r="E64" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F64" t="str">
         <v>-</v>
@@ -2477,7 +2477,7 @@
         <v>mark_bl_charges_reviewed(text,uuid) -&gt; jsonb (019; DEFINER; active user): moves calculations/B/L to reviewed and audits; hooks invalidate lines, B/Ls and pendencies.</v>
       </c>
       <c r="E65" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F65" t="str">
         <v>-</v>
@@ -2492,7 +2492,7 @@
         <v>src/services/charges/chargeOperationsService.ts; supabase/migrations/019_local_charges_manual_and_status_workflow.sql</v>
       </c>
       <c r="J65" t="str">
-        <v>-</v>
+        <v>Verified by code read — SQL/trigger/cron/edge or live-DB RLS surface with no executable assertion in this environment (static is the strongest method available).</v>
       </c>
     </row>
     <row r="66">
@@ -2509,7 +2509,7 @@
         <v>mark_bl_ready_for_billing(text,uuid) -&gt; jsonb (129; DEFINER; active user; anon revoked): revalidates canonical gate, customer, pending/USD lines, positive BRL value and an active charge table; updates calculations/B/L; audits; may trigger auto-issue.</v>
       </c>
       <c r="E66" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F66" t="str">
         <v>-</v>
@@ -2541,7 +2541,7 @@
         <v>mark_bl_ready_and_create_invoice(text,bigint,date,text,uuid) -&gt; jsonb (102_mark_ready_and_invoice_atomic.sql; INVOKER; active+admin): marks ready and creates invoice+ledger in one transaction; any failure rolls back both.</v>
       </c>
       <c r="E67" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F67" t="str">
         <v>-</v>
@@ -2556,7 +2556,7 @@
         <v>src/services/billing.ts; supabase/migrations/102_mark_ready_and_invoice_atomic.sql</v>
       </c>
       <c r="J67" t="str">
-        <v>-</v>
+        <v>Verified by code read — SQL/trigger/cron/edge or live-DB RLS surface with no executable assertion in this environment (static is the strongest method available).</v>
       </c>
     </row>
     <row r="68">
@@ -2570,10 +2570,10 @@
         <v>As the platform I reapply the review gate to a batch after import</v>
       </c>
       <c r="D68" t="str">
-        <v>apply_bl_review_gate_after_import(text[],uuid) -&gt; integer (129; DEFINER; active user): recomputes pendencies only for the batch B/Ls, updates bls/audit_logs/queue; never reopens invoiced historical B/Ls. No direct frontend caller remains — the import RPCs apply the gate internally.</v>
+        <v>apply_bl_review_gate_after_import(text[],uuid) -&gt; integer (129; DEFINER; active user): recomputes pendencies only for the batch B/Ls, updates bls/audit_logs/queue; never reopens invoiced historical B/Ls. It has no direct frontend caller by design — the import RPCs invoke it internally (migrations 129, 144, 149, 161).</v>
       </c>
       <c r="E68" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F68" t="str">
         <v>-</v>
@@ -2588,7 +2588,7 @@
         <v>supabase/migrations/129_review_gate_hardening.sql</v>
       </c>
       <c r="J68" t="str">
-        <v>Confirm the function is still reachable (called inside import RPCs) or an orphan candidate.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="69">
@@ -2605,7 +2605,7 @@
         <v>list_customer_reconciliation_queue(text,int) (025; reader guarded by 151), approve_customer_reconciliation(bigint,bigint,text,uuid) and reject_customer_reconciliation(bigint,text,uuid) (025; DEFINER; active user): approve links/updates B/L and contact; reject records reason; both audit and invalidate queue/operations/billing/B/L caches.</v>
       </c>
       <c r="E69" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F69" t="str">
         <v>-</v>
@@ -2637,7 +2637,7 @@
         <v>promote_calculated_bl_ready_for_billing() BEFORE INSERT/UPDATE on bls (129): promotes calculated -&gt; ready only when canonical gate, customer, BRL value and currencies allow; EXECUTE revoked from clients.</v>
       </c>
       <c r="E70" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F70" t="str">
         <v>-</v>
@@ -2669,7 +2669,7 @@
         <v>prevent_pending_review_invoice() BEFORE INSERT/UPDATE OF financial_status on bls (129): blocks financial_status='invoiced' while review or canonical pendencies remain.</v>
       </c>
       <c r="E71" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F71" t="str">
         <v>-</v>
@@ -2701,7 +2701,7 @@
         <v>guard_container_bl_without_containers() AFTER I/U on bls (064) creates a synthetic pendency so an empty container B/L cannot stay calculated/ready; ensure_container_bl_charge_status_default() (065) converts NULL charge_status of CNTR B/Ls to not_calculated; populate_charge_calculation_billing_metadata() (025) fills manifest and commercial-rule version on charge_calculations.</v>
       </c>
       <c r="E72" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F72" t="str">
         <v>-</v>
@@ -2716,7 +2716,7 @@
         <v>supabase/migrations/064_fix_granite_invoice_cancel_reissue.sql; supabase/migrations/065_fix_null_charge_status_cntr.sql; supabase/migrations/025_billing_orchestration_portal.sql</v>
       </c>
       <c r="J72" t="str">
-        <v>-</v>
+        <v>Verified by code read — SQL/trigger/cron/edge or live-DB RLS surface with no executable assertion in this environment (static is the strongest method available).</v>
       </c>
     </row>
     <row r="73">
@@ -2733,7 +2733,7 @@
         <v>charge_tables, charge_table_items, customer_rate_overrides: all operations admin-only (010+014). charge_calculations: SELECT admin (014), INSERT/UPDATE active (010), DELETE admin. customer_reconciliation_queue guarded via RPCs.</v>
       </c>
       <c r="E73" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F73" t="str">
         <v>-</v>
@@ -2748,7 +2748,7 @@
         <v>supabase/migrations/010_rls_by_role.sql; supabase/migrations/014_lock_down_financial_reads_and_audit_writes.sql</v>
       </c>
       <c r="J73" t="str">
-        <v>-</v>
+        <v>Verified by code read — SQL/trigger/cron/edge or live-DB RLS surface with no executable assertion in this environment (static is the strongest method available).</v>
       </c>
     </row>
     <row r="74">
@@ -2765,7 +2765,7 @@
         <v>Faturamento.tsx (useBilling/useBillingLedger): validation/bottleneck view of B/Ls, individual and consolidated issuance, invoice list; InvoiceDetailModal registers payments, cancels, refunds and prints; all financial writes go through admin-guarded RPCs; caches for invoices/receivables/B/Ls/customers/alerts invalidated.</v>
       </c>
       <c r="E74" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F74" t="str">
         <v>-</v>
@@ -2797,7 +2797,7 @@
         <v>create_invoice_from_bls_with_ledger(text[],bigint,date,text,boolean,uuid) -&gt; jsonb (100 + secure wrapper 141_secure_billing_core_wrappers.sql; active+admin): validates caller, runs the revoked core and link_invoice_to_ledger; frontend persists PIX payload as fallback. Legacy create_invoice_from_bls remains (020) behind the same wrapper hardening.</v>
       </c>
       <c r="E75" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F75" t="str">
         <v>-</v>
@@ -2829,7 +2829,7 @@
         <v>create_local_consolidated_invoice(bigint,bigint[],date,text,uuid) -&gt; jsonb (083_portal_ledger_alignment.sql; DEFINER; active+admin; wrapper -&gt; private core): creates the consolidated invoice, invoice_receivable_links and lifecycle event; rejects receivables already in an open consolidation.</v>
       </c>
       <c r="E76" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F76" t="str">
         <v>-</v>
@@ -2861,7 +2861,7 @@
         <v>mark_bls_ready_and_create_invoice (133_mark_bls_ready_and_create_invoice_atomic.sql; active+admin): batch variant that marks B/Ls ready and creates the invoice in one transaction.</v>
       </c>
       <c r="E77" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F77" t="str">
         <v>-</v>
@@ -2893,7 +2893,7 @@
         <v>run_billing_for_import_batch (149_remove_billing_from_import_function.sql; active+admin): executes the billing step decoupled from the manifest import function.</v>
       </c>
       <c r="E78" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F78" t="str">
         <v>-</v>
@@ -2925,7 +2925,7 @@
         <v>list_invoice_details(bigint) -&gt; jsonb (020; INVOKER; active+admin): reads invoice, B/Ls, items and payments; the client complements consolidated breakdown and backfills PIX best-effort.</v>
       </c>
       <c r="E79" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F79" t="str">
         <v>-</v>
@@ -2957,7 +2957,7 @@
         <v>get_consolidated_invoice_item_breakdown(bigint) -&gt; table (090_restrict_consolidated_invoice_breakdown.sql; DEFINER; active+admin; PUBLIC revoked): protected read of calculations behind a consolidated invoice; client falls back to aggregate if shape/sum does not reconcile.</v>
       </c>
       <c r="E80" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F80" t="str">
         <v>-</v>
@@ -2989,7 +2989,7 @@
         <v>register_invoice_payment(bigint,numeric,text,timestamptz,text,uuid) (020; INVOKER; active+admin) inserts payment and updates invoice/B/L status; register_ledger_invoice_payment (8 args; 111_pix_exact_and_manual_overpayment_refunds.sql; DEFINER; active+admin) allocates in the ledger, updates receivables/links/invoice/B/Ls, writes lifecycle events and creates a refund for manual overpayment; PIX-exact rules enforced.</v>
       </c>
       <c r="E81" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F81" t="str">
         <v>-</v>
@@ -3021,7 +3021,7 @@
         <v>cancel_invoice(bigint,text,uuid) -&gt; jsonb (064 + wrapper 142_secure_cancel_invoice_wrapper.sql; DEFINER; active+admin): cancels an invoice without payments, updates batch and B/L/Granito financial state and audits; also used by the vehicle flow to release an exempt B/L.</v>
       </c>
       <c r="E82" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F82" t="str">
         <v>-</v>
@@ -3053,7 +3053,7 @@
         <v>add_manual_invoice_charge(bigint,text,numeric,numeric,text,uuid) and delete_manual_invoice_charge(bigint,uuid) (108; INVOKER; active+admin): mutate manual items of an open invoice, recalculate totals, clear/regenerate PIX payload per state and audit.</v>
       </c>
       <c r="E83" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F83" t="str">
         <v>-</v>
@@ -3085,7 +3085,7 @@
         <v>list_consolidatable_receivables (066), list_invoice_refunds (112; STABLE INVOKER), settle_invoice_refund (112; DEFINER; active+admin; pending-&gt;settled with audit), backfill_invoice_receivable_links (066/067), link_invoice_to_ledger and sync_local_charge_receivable (ledger maintenance called by billing flows).</v>
       </c>
       <c r="E84" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F84" t="str">
         <v>-</v>
@@ -3117,7 +3117,7 @@
         <v>detect_overdue_invoices() -&gt; integer (024; DEFINER; guard added by 151): marks overdue local invoices and creates non-duplicate alerts; callable from alerts.ts.</v>
       </c>
       <c r="E85" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F85" t="str">
         <v>-</v>
@@ -3149,7 +3149,7 @@
         <v>assign_invoice_number() BEFORE INSERT on invoices (003) fills the annual sequential number; fn_block_invoice_overdue_customer() (031) blocks a new invoice when the customer has an overdue local invoice; prevent_duplicate_active_invoice_bl_link() (064) rejects a second active/paid link for the same B/L.</v>
       </c>
       <c r="E86" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F86" t="str">
         <v>-</v>
@@ -3164,7 +3164,7 @@
         <v>supabase/migrations/003_functions.sql; supabase/migrations/031_overdue_enforcement.sql; supabase/migrations/064_fix_granite_invoice_cancel_reissue.sql</v>
       </c>
       <c r="J86" t="str">
-        <v>-</v>
+        <v>Verified by code read — SQL/trigger/cron/edge or live-DB RLS surface with no executable assertion in this environment (static is the strongest method available).</v>
       </c>
     </row>
     <row r="87">
@@ -3181,7 +3181,7 @@
         <v>pg_cron job mark-overdue-invoices (06:00 UTC; 031) runs mark_overdue_invoices() over local invoices; demurrage was removed from overdue enforcement by 157_demurrage_drop_overdue.sql (demurrage has no due_date/overdue).</v>
       </c>
       <c r="E87" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F87" t="str">
         <v>-</v>
@@ -3213,7 +3213,7 @@
         <v>emit_invoice_on_bl_ready() AFTER I/U OF charge_status on bls (070_ledger_individual_invoice_rpc.sql): syncs the receivable and attempts a best-effort individual invoice; failure becomes audit_logs.auto_invoice_failed without aborting the transition.</v>
       </c>
       <c r="E88" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F88" t="str">
         <v>-</v>
@@ -3245,7 +3245,7 @@
         <v>mark_obsolete_consolidated_links() AFTER UPDATE OF status on invoices (073) obsoletes all active links; mark_replaced_obsolete_consolidated_invoice() AFTER INSERT of an active link (076) chains the obsolete invoice to its replacement; ledger settlement guards (ledgerSettlementGuardsMigration) protect settlement invariants.</v>
       </c>
       <c r="E89" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F89" t="str">
         <v>-</v>
@@ -3277,7 +3277,7 @@
         <v>populate_local_invoice_pix_payload() BEFORE I/U on invoices (074) generates the PIX payload for local individual/consolidated invoices; keep_single_pix_txid_settlement_row() BEFORE INSERT on ledger_settlements (075) stores the TXID only on the first row of a consolidated payment.</v>
       </c>
       <c r="E90" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F90" t="str">
         <v>-</v>
@@ -3309,7 +3309,7 @@
         <v>Invoice documents are print-ready React components sharing InvoiceDocumentKit.tsx (header/title/client/footer); print rules live in src/index.css and the file is produced by window.print(); PIX payload rendered as QR via qrcode.react and src/lib/pix.ts.</v>
       </c>
       <c r="E91" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F91" t="str">
         <v>-</v>
@@ -3341,7 +3341,7 @@
         <v>invoices, payments, invoice_bls, billing_batches (SELECT active per 041), bl_receivables and invoice_receivable_links: financial families are admin-only for writes (and mostly for reads) per 010+014+020 and the ledger migrations; operational surfaces read through RPCs.</v>
       </c>
       <c r="E92" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F92" t="str">
         <v>-</v>
@@ -3356,7 +3356,7 @@
         <v>supabase/migrations/014_lock_down_financial_reads_and_audit_writes.sql; supabase/migrations/020_billing_hybrid_workflow.sql; supabase/migrations/041_rls_missing_tables.sql</v>
       </c>
       <c r="J92" t="str">
-        <v>-</v>
+        <v>Verified by code read — SQL/trigger/cron/edge or live-DB RLS surface with no executable assertion in this environment (static is the strongest method available).</v>
       </c>
     </row>
     <row r="93">
@@ -3373,7 +3373,7 @@
         <v>Demurrage.tsx tracks container discharge/return per B/L, lists demurrage invoices with tabs, shows a PTAX staleness banner and an 'Informar PTAX' modal that calls recalculate_demurrage_invoices_manual; voyage filter uses VoyageCombobox (clearable); KPIs from demurrageKpis.ts.</v>
       </c>
       <c r="E93" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F93" t="str">
         <v>-</v>
@@ -3405,7 +3405,7 @@
         <v>DemurrageRates.tsx CRUDs demurrage_rates via demurrageRates.ts (delete behind confirm dialog); rates configurable per container type with temporal validity; active flag = immediate deactivation, valid_to = scheduled expiry; RLS: SELECT active, mutations admin.</v>
       </c>
       <c r="E94" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F94" t="str">
         <v>-</v>
@@ -3437,7 +3437,7 @@
         <v>src/App.tsx renders Navigate to /demurrage with replace.</v>
       </c>
       <c r="E95" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F95" t="str">
         <v>-</v>
@@ -3452,7 +3452,7 @@
         <v>src/App.tsx</v>
       </c>
       <c r="J95" t="str">
-        <v>-</v>
+        <v>Verified by code read — SQL/trigger/cron/edge or live-DB RLS surface with no executable assertion in this environment (static is the strongest method available).</v>
       </c>
     </row>
     <row r="96">
@@ -3469,7 +3469,7 @@
         <v>calculateDemurrage: days between discharge and return minus free time; free time override affects only the start of billing (P1 begins at override+1) while P1/P2 band boundaries stay fixed by the rate group; return-before-discharge rejected in calculation, UI/import and DB constraint; USD discounts applied before conversion; markup 1.065 is a single canonical constant; rate precedence: B/L override &gt; active valid db rate (no static fallback).</v>
       </c>
       <c r="E96" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F96" t="str">
         <v>-</v>
@@ -3501,7 +3501,7 @@
         <v>create_demurrage_invoice_with_items (132_create_demurrage_invoice_atomic.sql; issuance semantics per 156_demurrage_create_invoice_issued.sql): creates invoice + frozen USD line items atomically (free days, P1/P2 days and rates per item); only issuable when every container of the B/L has returned; USD locked at issuance; the initial recalculation snapshot is written to demurrage_invoice_history at issuance.</v>
       </c>
       <c r="E97" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F97" t="str">
         <v>-</v>
@@ -3533,7 +3533,7 @@
         <v>recalculate_demurrage_invoices(p_ptax,p_quote_date,p_source) (155_demurrage_recalculate_rpcs.sql; SECURITY DEFINER; no auth.uid() check; executable only by service_role): applies markup 1.065 in the DB, updates current_roe/current_total_brl of unpaid invoices and appends an immutable demurrage_invoice_history row only when the PTAX actually changes (event_date = quote date).</v>
       </c>
       <c r="E98" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F98" t="str">
         <v>-</v>
@@ -3542,7 +3542,7 @@
         <v>-</v>
       </c>
       <c r="H98" t="str">
-        <v>Static</v>
+        <v>SQL-contract: demurrageRecalcAndPixWindowMigration.test.ts</v>
       </c>
       <c r="I98" t="str">
         <v>supabase/migrations/155_demurrage_recalculate_rpcs.sql; supabase/migrations/154_demurrage_rename_frozen_to_current.sql</v>
@@ -3565,7 +3565,7 @@
         <v>recalculate_demurrage_invoices_manual (155; authenticated wrapper requiring is_active_user()): same recalculation core, driven by the 'Informar PTAX' modal on /demurrage.</v>
       </c>
       <c r="E99" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F99" t="str">
         <v>-</v>
@@ -3574,7 +3574,7 @@
         <v>-</v>
       </c>
       <c r="H99" t="str">
-        <v>Static</v>
+        <v>SQL-contract: demurrageRecalcAndPixWindowMigration.test.ts</v>
       </c>
       <c r="I99" t="str">
         <v>src/services/demurrage/; supabase/migrations/155_demurrage_recalculate_rpcs.sql</v>
@@ -3597,7 +3597,7 @@
         <v>get_demurrage_recent_values(p_invoice_id bigint, p_date date) (158_demurrage_pix_window_conciliation.sql; anon revoked; authenticated granted): returns the two most recent demurrage_invoice_history entries with event_date &lt;= payment date, implementing the ADR 0015 two-PTAX window.</v>
       </c>
       <c r="E100" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F100" t="str">
         <v>-</v>
@@ -3606,7 +3606,7 @@
         <v>-</v>
       </c>
       <c r="H100" t="str">
-        <v>Static</v>
+        <v>SQL-contract: demurrageRecalcAndPixWindowMigration.test.ts</v>
       </c>
       <c r="I100" t="str">
         <v>supabase/migrations/158_demurrage_pix_window_conciliation.sql</v>
@@ -3629,7 +3629,7 @@
         <v>save_bl_demurrage_config (147_save_bl_demurrage_config_atomic.sql; active user): saves free-time override and related config for a B/L in one call with audit; called from BlDemurrageSection.</v>
       </c>
       <c r="E101" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F101" t="str">
         <v>-</v>
@@ -3661,7 +3661,7 @@
         <v>Edge Function recalc-demurrage-ptax: requires Authorization bearer exactly equal to SUPABASE_SERVICE_ROLE_KEY (timing-safe compare); queries BCB CotacaoDolarPeriodo for the last ~10 days, top 1 by dataHoraCotacao desc (never 'today only', so weekends/holidays return the latest quote); passes raw cotacaoVenda to recalculate_demurrage_invoices (markup applied in DB); aborts with error only on HTTP/network failure or empty period; designed to be scheduled weekdays ~14h BRT.</v>
       </c>
       <c r="E102" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F102" t="str">
         <v>-</v>
@@ -3693,7 +3693,7 @@
         <v>set_container_discharge_date() BEFORE INSERT on bl_containers without discharge copies voyages.ata (028); 138_audit_container_dates_and_propagate_ata.sql audits date changes and propagates voyage ATA updates to containers.</v>
       </c>
       <c r="E103" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F103" t="str">
         <v>-</v>
@@ -3725,7 +3725,7 @@
         <v>demurrage_rates: SELECT active, mutations admin. demurrage_invoices/demurrage_invoice_items (050 final): active read/insert/update, admin delete. demurrage_invoice_history (160_demurrage_invoice_history_rls_active.sql): SELECT restricted to is_active_user() — fixing the permissive USING(true) SELECT that 153 had created — and writes only via SECURITY DEFINER RPCs.</v>
       </c>
       <c r="E104" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F104" t="str">
         <v>-</v>
@@ -3757,7 +3757,7 @@
         <v>Reconciliacao.tsx: dropzone upload of the bank spreadsheet; parsing extracts transactions and normalizes TXIDs; matching separates safe matches from ambiguities; the operator confirms the batch; history table with pagination/export; reversal entry points.</v>
       </c>
       <c r="E105" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F105" t="str">
         <v>-</v>
@@ -3786,10 +3786,10 @@
         <v>As the platform I match demurrage payments by txid with the two-PTAX window</v>
       </c>
       <c r="D106" t="str">
-        <v>Per ADR 0015 (158_demurrage_pix_window_conciliation.sql): primary identification by txid = doc_number (normalized); value validated against the two most recent demurrage_invoice_history entries with event_date &lt;= payment date (R$0.01 tolerance); fallback CNPJ + same window; only full settlement (no partial demurrage payments); non-matching values become manual divergences; the matched value is frozen with source='payment' and paid_at set, ending recalculation for that invoice.</v>
+        <v>Per ADR 0015 (158_demurrage_pix_window_conciliation.sql): identification is by txid = doc_number (normalized) only — there is no CNPJ fallback (matchType is 'txid' | 'unmatched' in reconciliacao.ts, and 158 has no CNPJ path); the paid value is validated against the two most recent demurrage_invoice_history entries with event_date &lt;= payment date (R$0.01 tolerance), and the frontend additionally accepts the invoice's current total_brl; only full settlement (no partial demurrage payments); unmatched txids stay unmatched and value mismatches become ambiguous/manual; the matched value is frozen with source='payment' and paid_at set, ending recalculation for that invoice.</v>
       </c>
       <c r="E106" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F106" t="str">
         <v>-</v>
@@ -3798,7 +3798,7 @@
         <v>-</v>
       </c>
       <c r="H106" t="str">
-        <v>Static</v>
+        <v>SQL-contract: demurrageRecalcAndPixWindowMigration.test.ts</v>
       </c>
       <c r="I106" t="str">
         <v>supabase/migrations/158_demurrage_pix_window_conciliation.sql; src/services/reconciliacao.ts</v>
@@ -3821,7 +3821,7 @@
         <v>confirm_unified_pix_matches(jsonb) -&gt; jsonb (103; demurrage leg rewritten by 158): local invoices reconciled by TXID/value through the guarded ledger RPC; demurrage through confirm_demurrage_pix_matches with the two-PTAX window; a single transaction — any error aborts the whole batch; caller invalidates invoices, demurrage, B/Ls, customers and history.</v>
       </c>
       <c r="E107" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F107" t="str">
         <v>-</v>
@@ -3853,7 +3853,7 @@
         <v>reconcile_invoice_payment_by_txid(text,numeric,timestamptz) -&gt; jsonb (067; DEFINER; active+admin): strict TXID match; records payment/settlement and updates invoice/receivables.</v>
       </c>
       <c r="E108" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F108" t="str">
         <v>-</v>
@@ -3868,7 +3868,7 @@
         <v>src/services/billingLedger.ts; supabase/migrations/067_local_billing_ledger_phase2.sql</v>
       </c>
       <c r="J108" t="str">
-        <v>-</v>
+        <v>Verified by code read; the opt-in integration suite covers it but was not executed in this environment.</v>
       </c>
     </row>
     <row r="109">
@@ -3885,7 +3885,7 @@
         <v>reverse_invoice_payment(bigint,text,uuid) -&gt; jsonb (final def 118_fix_bls_financial_status_on_reversal.sql; DEFINER; active+admin; mandatory justification): reverses settlement/payment, reopens receivables/links, fixes invoice status and bls.financial_status, clears PIX effects (108) and audits.</v>
       </c>
       <c r="E109" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F109" t="str">
         <v>-</v>
@@ -3917,7 +3917,7 @@
         <v>reverse_demurrage_payment(bigint,text,uuid) -&gt; jsonb (113 + 131_clear_demurrage_extract_flag_on_reversal.sql; DEFINER; active+admin; mandatory justification): removes the demurrage settlement, reverts invoice status, clears the extract-matched flag and audits.</v>
       </c>
       <c r="E110" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F110" t="str">
         <v>-</v>
@@ -3949,7 +3949,7 @@
         <v>src/App.tsx renders Navigate to /reconciliacao with replace.</v>
       </c>
       <c r="E111" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F111" t="str">
         <v>-</v>
@@ -3964,7 +3964,7 @@
         <v>src/App.tsx</v>
       </c>
       <c r="J111" t="str">
-        <v>-</v>
+        <v>Verified by code read — SQL/trigger/cron/edge or live-DB RLS surface with no executable assertion in this environment (static is the strongest method available).</v>
       </c>
     </row>
     <row r="112">
@@ -3981,7 +3981,7 @@
         <v>PortalLogin.tsx + usePortalAuth.signIn: a document identifier is resolved to the technical email via portal_resolve_login(text); authentication is supabasePortal.auth.signInWithPassword; P0429 keeps a specific rate-limit message, all other failures become a generic credentials error; success hydrates the overview and unlocks PortalProtectedRoute redirecting to /portal.</v>
       </c>
       <c r="E112" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F112" t="str">
         <v>-</v>
@@ -4013,7 +4013,7 @@
         <v>portal_resolve_login(text) -&gt; text (122_harden_portal_resolve_login.sql; DEFINER; the only anon pre-auth exception per ADR 0013): logs the attempt by identifier hash, applies an attempt window and returns a generic error; resolves document -&gt; technical email; creates no session.</v>
       </c>
       <c r="E113" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F113" t="str">
         <v>-</v>
@@ -4045,7 +4045,7 @@
         <v>PortalForgotPassword.tsx resolves documents via portal_resolve_login (emails used directly) and calls supabasePortal.auth.resetPasswordForEmail; success and non-rate-limited failures render the same non-enumerating message.</v>
       </c>
       <c r="E114" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F114" t="str">
         <v>-</v>
@@ -4077,7 +4077,7 @@
         <v>PortalResetPassword.tsx reads access_token/refresh_token/type=recovery from the URL hash, establishes the session via setSession, strips tokens from the URL and allows updateUser({password}) after validating min 8 chars + confirmation.</v>
       </c>
       <c r="E115" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F115" t="str">
         <v>-</v>
@@ -4109,7 +4109,7 @@
         <v>PortalDashboard.tsx loads portal_get_session_overview_v2() (115; DEFINER; requires auth.uid() + active linked account; updates last_login_at) and the ShipScheduleWidget reading vessel_schedules with Realtime invalidation.</v>
       </c>
       <c r="E116" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F116" t="str">
         <v>-</v>
@@ -4141,7 +4141,7 @@
         <v>PortalBilling.tsx via portalBilling.ts: portal_list_invoices, portal_invoice_details, portal_list_consolidatable_receivables, portal_list_demurrage_invoices, portal_get_demurrage_invoice_detail — all scoped by current_portal_customer_id() and gated by CE Mercante (123_portal_ce_mercante_gate.sql; demurrage reference added by 159); consolidation modal creates/obsoletes consolidations.</v>
       </c>
       <c r="E117" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F117" t="str">
         <v>-</v>
@@ -4173,7 +4173,7 @@
         <v>portal_create_consolidation(bigint[]) -&gt; jsonb (123; DEFINER): validates ownership, CE gate and rate limit 3/10min; creates the consolidated invoice via the internal core, inserts an internal alert and an in-app notification; hooks invalidate receivables/invoices and refresh the overview.</v>
       </c>
       <c r="E118" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F118" t="str">
         <v>-</v>
@@ -4205,7 +4205,7 @@
         <v>portal_obsolete_consolidation(bigint) -&gt; jsonb (119_portal_fixes_post_pr227.sql; DEFINER): requires ownership, obsoletable status and zero payments; rate limit 3/15min; obsoletes invoice + links, records lifecycle, alert and notification (ADR 0002).</v>
       </c>
       <c r="E119" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F119" t="str">
         <v>-</v>
@@ -4237,7 +4237,7 @@
         <v>portal_open_demurrage_dispute(bigint,text) -&gt; jsonb (117_portal_fase3_rate_limiting.sql; DEFINER): own invoice + reason required; rate limit 3/30min; updates dispute state, inserts customer notification and internal alert; disputes never block recalculation or payment.</v>
       </c>
       <c r="E120" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F120" t="str">
         <v>-</v>
@@ -4269,7 +4269,7 @@
         <v>PortalOperacao.tsx via portal_list_operation_bls() (123; STABLE DEFINER; customer scope + CE gate): lists own B/Ls; containers and free-time/demurrage indicators derived client-side; export covers only the customer-filtered set.</v>
       </c>
       <c r="E121" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F121" t="str">
         <v>-</v>
@@ -4301,7 +4301,7 @@
         <v>PortalProfile.tsx via portal_get_profile() (116) and portal_update_profile (119; 6 optional text args): updates only account email, customer address and contact phone; overview reloaded after save.</v>
       </c>
       <c r="E122" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F122" t="str">
         <v>-</v>
@@ -4333,7 +4333,7 @@
         <v>portal_list_notifications(int=20) (119), portal_notification_unread_count() (116; 30s polling), portal_mark_notification_read(bigint) and portal_mark_all_notifications_read() (116) — all scoped by current_portal_customer_id(); NotificationBell consumes list+counter and invalidates on mutation.</v>
       </c>
       <c r="E123" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F123" t="str">
         <v>-</v>
@@ -4365,7 +4365,7 @@
         <v>trg_notify_invoice_issued (invoices status -&gt; issued), trg_notify_demurrage_issued (demurrage_invoices) and trg_notify_dispute_responded (dispute_status -&gt; resolvido) insert portal_notifications rows (116_portal_fase2_notifications_disputes_profile.sql); this in-app path is the active customer notification mechanism (email is off by decision).</v>
       </c>
       <c r="E124" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F124" t="str">
         <v>-</v>
@@ -4380,7 +4380,7 @@
         <v>supabase/migrations/116_portal_fase2_notifications_disputes_profile.sql</v>
       </c>
       <c r="J124" t="str">
-        <v>-</v>
+        <v>Verified by code read — SQL/trigger/cron/edge or live-DB RLS surface with no executable assertion in this environment (static is the strongest method available).</v>
       </c>
     </row>
     <row r="125">
@@ -4397,7 +4397,7 @@
         <v>provision-portal-user: verify_jwt=true (supabase/config.toml); validates the caller JWT via auth.getUser, requires an active internal profile with role admin/administrativo; CORS allowlist with origin rejection; persistent rate limit 20/h per user via check_provision_rate_limit; service role reads/updates customer_portal_accounts and uses Auth Admin createUser/updateUserById to create or reset the user and link auth_user_id/email; failures map to 401/403/429/400/404/409/500; the frontend requires auth_user_id before activating the account.</v>
       </c>
       <c r="E125" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F125" t="str">
         <v>-</v>
@@ -4429,7 +4429,7 @@
         <v>notify-invoice-issued: bearer must equal SUPABASE_SERVICE_ROLE_KEY (timing-safe); accepts absent Origin or Origin == SUPABASE_URL; service role re-reads invoices/customers/customer_contacts (no DB writes) and sends via Resend; missing recipient/key -&gt; skipped/sent:false; auth failure 401; Resend/parse failure 500. No functions.invoke caller exists in src and no webhook is configured in the repo — inactive by decision; customer notification is in-app via trg_notify_invoice_issued.</v>
       </c>
       <c r="E126" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F126" t="str">
         <v>-</v>
@@ -4461,7 +4461,7 @@
         <v>current_portal_customer_id() resolves the customer from auth.uid() and raises on null; all portal_* data RPCs use it; anon EXECUTE was re-revoked from the six portal read RPCs by 150_revoke_anon_portal_read_rpcs.sql, restoring the ADR 0013 allowlist (portal_resolve_login only); PortalProtectedRoute + isolated storageKey keep the session separate from staff.</v>
       </c>
       <c r="E127" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F127" t="str">
         <v>-</v>
@@ -4493,7 +4493,7 @@
         <v>Granite.tsx: selects a voyage, parses the COSCO cargo/booking report (graniteImport.ts), reconciles shipper -&gt; customer, persists granite_manifests/granite_bls via import_granite_manifest_transactional (136; atomic), calculates weight/B/L charges into granite_bl_charges (graniteCharges.ts + granite_rates precedence) and issues shared invoices downstream.</v>
       </c>
       <c r="E128" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F128" t="str">
         <v>-</v>
@@ -4525,7 +4525,7 @@
         <v>GraniteRates.tsx CRUDs granite_rates via graniteCharges.ts services; activation affects future calculations; RLS 042 final: active read/insert/update, admin delete.</v>
       </c>
       <c r="E129" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F129" t="str">
         <v>-</v>
@@ -4557,7 +4557,7 @@
         <v>create_invoice_from_granite_bls (064_fix_granite_invoice_cancel_reissue.sql; DEFINER; active+admin): creates invoice/items/invoice_granite_bls links, updates granite_bls status and audits; avoids a duplicate active invoice; classification refined by 137_classify_granite_invoices.sql.</v>
       </c>
       <c r="E130" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F130" t="str">
         <v>-</v>
@@ -4589,7 +4589,7 @@
         <v>save_granite_bl_review (148_save_granite_bl_review_atomic.sql; active user): saves the granite review (customer link/status) atomically with audit; surfaces in the unified /revisao queue.</v>
       </c>
       <c r="E131" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F131" t="str">
         <v>-</v>
@@ -4621,7 +4621,7 @@
         <v>prevent_duplicate_active_invoice_granite_bl_link() BEFORE I/U on invoice_granite_bls (064) rejects a second active/paid link for the same granite B/L.</v>
       </c>
       <c r="E132" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F132" t="str">
         <v>-</v>
@@ -4636,7 +4636,7 @@
         <v>supabase/migrations/064_fix_granite_invoice_cancel_reissue.sql</v>
       </c>
       <c r="J132" t="str">
-        <v>-</v>
+        <v>Verified by code read — SQL/trigger/cron/edge or live-DB RLS surface with no executable assertion in this environment (static is the strongest method available).</v>
       </c>
     </row>
     <row r="133">
@@ -4653,7 +4653,7 @@
         <v>granite_manifests, granite_bls, granite_bl_charges, granite_rates (042 final + 050 alignment): active users read/insert/update; admin deletes; invoice_granite_bls follows the financial family.</v>
       </c>
       <c r="E133" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F133" t="str">
         <v>-</v>
@@ -4668,7 +4668,7 @@
         <v>supabase/migrations/042_rls_module_hardening.sql; supabase/migrations/050_alignment_granite_portal_demurrage.sql</v>
       </c>
       <c r="J133" t="str">
-        <v>-</v>
+        <v>Verified by code read — SQL/trigger/cron/edge or live-DB RLS surface with no executable assertion in this environment (static is the strongest method available).</v>
       </c>
     </row>
     <row r="134">
@@ -4685,7 +4685,7 @@
         <v>Clientes.tsx: summary cards; search by name/fantasy/document; filters by email/B-L/balance; 50-row paginated sortable table; admin-only selection and controlled deletion; create modal; base import with preview; XLSX export via exports.ts.</v>
       </c>
       <c r="E134" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F134" t="str">
         <v>-</v>
@@ -4717,7 +4717,7 @@
         <v>ClienteFicha.tsx edits the record and contacts (customers.ts/customerBase.ts) and manages the Portal account: upsert_customer_portal_account creates the initially-inactive account, the Edge Function provisions the Auth user, and only then set_customer_portal_account_active can activate; invalidates record and lists.</v>
       </c>
       <c r="E135" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F135" t="str">
         <v>-</v>
@@ -4749,7 +4749,7 @@
         <v>create_customer_with_contacts (143_create_customer_with_contacts_atomic.sql; active user): creates customer + contacts in one transaction with audit.</v>
       </c>
       <c r="E136" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F136" t="str">
         <v>-</v>
@@ -4781,7 +4781,7 @@
         <v>update_customer_with_audit (134_atomic_customer_update_audit.sql; active user): applies the change set and writes the audit rows atomically.</v>
       </c>
       <c r="E137" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F137" t="str">
         <v>-</v>
@@ -4813,7 +4813,7 @@
         <v>deleteCustomers pre-checks dependencies (B/Ls, invoices, receivables, portal accounts) via deleteDependencies.ts, reports blocked vs deletable, cascades operational children bottom-up and audits best-effort via deleteAudit.ts (ADR 0009); RLS keeps DELETE admin-only.</v>
       </c>
       <c r="E138" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F138" t="str">
         <v>-</v>
@@ -4845,7 +4845,7 @@
         <v>get_customer_portal_account(bigint) (129; STABLE DEFINER; active+admin) reads account + Auth state; upsert_customer_portal_account (129; active+admin) creates/updates an initially-inactive account; set_customer_portal_account_active(bigint,boolean,uuid) (129; active+admin) toggles activation and refuses to activate without auth_user_id/email.</v>
       </c>
       <c r="E139" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F139" t="str">
         <v>-</v>
@@ -4877,7 +4877,7 @@
         <v>customers and customer_contacts (010 final): active users read/insert/update; admin deletes; Portal profile writes go only through portal_update_profile; contact email participates in the review gate.</v>
       </c>
       <c r="E140" t="str">
-        <v>Spec'd</v>
+        <v>Verified</v>
       </c>
       <c r="F140" t="str">
         <v>-</v>
@@ -4892,7 +4892,7 @@
         <v>supabase/migrations/010_rls_by_role.sql</v>
       </c>
       <c r="J140" t="str">
-        <v>-</v>
+        <v>Verified by code read — SQL/trigger/cron/edge or live-DB RLS surface with no executable assertion in this environment (static is the strongest method available).</v>
       </c>
     </row>
   </sheetData>
@@ -4945,7 +4945,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Status: Spec'd</v>
+        <v>Status: Verified</v>
       </c>
       <c r="B5">
         <v>139</v>

--- a/docs/spec/2026-07-02-behavioral-spec.xlsx
+++ b/docs/spec/2026-07-02-behavioral-spec.xlsx
@@ -461,7 +461,7 @@
         <v>Login.tsx form calls useAuth.signIn -&gt; supabase.auth.signInWithPassword on the internal client; useAuth loads the user_profiles row and exposes profile/capabilities; a missing or inactive profile keeps the user out of protected routes; on success Login.tsx navigates to /painel itself (an already-authenticated visitor is redirected by a Navigate guard); errors shown inline.</v>
       </c>
       <c r="E2" t="str">
-        <v>Verified</v>
+        <v>Verified (static)</v>
       </c>
       <c r="F2" t="str">
         <v>-</v>
@@ -557,7 +557,7 @@
         <v>src/services/supabase.ts creates two clients: supabase (staff) and supabasePortal with its own storageKey ('td-portal-auth') and detectSessionInUrl:false; the sessions coexist and logging out of one does not drop the other.</v>
       </c>
       <c r="E5" t="str">
-        <v>Verified</v>
+        <v>Verified (static)</v>
       </c>
       <c r="F5" t="str">
         <v>-</v>
@@ -621,7 +621,7 @@
         <v>RLS (010_rls_by_role.sql + later fixes): self/admin SELECT; a user updates only their own row and only while active; INSERT/DELETE admin-only. Helpers is_active_user()/is_admin()/current_user_role() underpin all role-based policies.</v>
       </c>
       <c r="E7" t="str">
-        <v>Verified</v>
+        <v>Verified (static)</v>
       </c>
       <c r="F7" t="str">
         <v>-</v>
@@ -653,7 +653,7 @@
         <v>prevent_user_profile_privilege_escalation() BEFORE UPDATE on user_profiles rejects a user changing their own role or active flag; service_role remains allowed for provisioning.</v>
       </c>
       <c r="E8" t="str">
-        <v>Verified</v>
+        <v>Verified (static)</v>
       </c>
       <c r="F8" t="str">
         <v>-</v>
@@ -877,7 +877,7 @@
         <v>The catch-all route in src/App.tsx renders Navigate to /painel with replace; the destination then applies the normal auth guards.</v>
       </c>
       <c r="E15" t="str">
-        <v>Verified</v>
+        <v>Verified (static)</v>
       </c>
       <c r="F15" t="str">
         <v>-</v>
@@ -909,7 +909,7 @@
         <v>count_distinct_containers() -&gt; bigint (045_count_distinct_containers_fn.sql), STABLE SECURITY INVOKER, PUBLIC revoked, authenticated granted; read-only aggregate. No frontend caller exists in src today.</v>
       </c>
       <c r="E16" t="str">
-        <v>Verified</v>
+        <v>Verified (static)</v>
       </c>
       <c r="F16" t="str">
         <v>-</v>
@@ -941,7 +941,7 @@
         <v>010_rls_by_role.sql: active users read/insert/update alerts; only admin deletes; alert writers include overdue detection and portal dispute flows.</v>
       </c>
       <c r="E17" t="str">
-        <v>Verified</v>
+        <v>Verified (static)</v>
       </c>
       <c r="F17" t="str">
         <v>-</v>
@@ -973,7 +973,7 @@
         <v>014_lock_down_financial_reads_and_audit_writes.sql: active users read; INSERT requires active profile and changed_by=auth.uid(); UPDATE/DELETE admin-only. audit_logs feeds B/L timeline, voyage timeline and admin observability.</v>
       </c>
       <c r="E18" t="str">
-        <v>Verified</v>
+        <v>Verified (static)</v>
       </c>
       <c r="F18" t="str">
         <v>-</v>
@@ -1005,7 +1005,7 @@
         <v>pg_cron job cleanup-portal-sessions (03:00 UTC, 041_rls_missing_tables.sql) deletes legacy portal sessions expired for more than one day.</v>
       </c>
       <c r="E19" t="str">
-        <v>Verified</v>
+        <v>Verified (static)</v>
       </c>
       <c r="F19" t="str">
         <v>-</v>
@@ -1037,7 +1037,7 @@
         <v>pg_cron job cleanup-provision-rate-limit (03:30 UTC, 053_security_hardening.sql) removes provision-portal-user rate-limit rows older than 2 days.</v>
       </c>
       <c r="E20" t="str">
-        <v>Verified</v>
+        <v>Verified (static)</v>
       </c>
       <c r="F20" t="str">
         <v>-</v>
@@ -1325,7 +1325,7 @@
         <v>trg_voyage_schedule_snapshot AFTER INSERT on audit_logs (POD/POL events) updates voyages JSONB snapshot; 052 fixed JSON null handling so a null new_value does not violate NOT NULL.</v>
       </c>
       <c r="E29" t="str">
-        <v>Verified</v>
+        <v>Verified (static)</v>
       </c>
       <c r="F29" t="str">
         <v>-</v>
@@ -1485,7 +1485,7 @@
         <v>124_vessel_schedules.sql (+ 139 grants): SELECT for any authenticated (portal-compatible by design); INSERT/UPDATE require active internal user; DELETE admin. ended_vessels: SELECT authenticated; INSERT active; DELETE admin; no UPDATE policy exists.</v>
       </c>
       <c r="E34" t="str">
-        <v>Verified</v>
+        <v>Verified (static)</v>
       </c>
       <c r="F34" t="str">
         <v>-</v>
@@ -1837,7 +1837,7 @@
         <v>validate_bl_breakbulk_item_parent() BEFORE INSERT/UPDATE on bl_breakbulk_items (006_breakbulk_module.sql) rejects items whose parent B/L cargo mode is not carga_solta.</v>
       </c>
       <c r="E45" t="str">
-        <v>Verified</v>
+        <v>Verified (static)</v>
       </c>
       <c r="F45" t="str">
         <v>-</v>
@@ -1933,7 +1933,7 @@
         <v>validate_vehicle_relationships() BEFORE INSERT/UPDATE on vehicles (004_vehicles.sql; search_path fixed later) normalizes fields and rejects incoherent voyage/B/L/container combinations.</v>
       </c>
       <c r="E48" t="str">
-        <v>Verified</v>
+        <v>Verified (static)</v>
       </c>
       <c r="F48" t="str">
         <v>-</v>
@@ -2189,7 +2189,7 @@
         <v>Final state of 010: bls, bl_containers, bl_breakbulk_items — active users read/insert/update; admin deletes. bls carries review gate, promotion and billing guards via triggers; bl_containers delete additionally blocked by service-level dependency checks.</v>
       </c>
       <c r="E56" t="str">
-        <v>Verified</v>
+        <v>Verified (static)</v>
       </c>
       <c r="F56" t="str">
         <v>-</v>
@@ -2477,7 +2477,7 @@
         <v>mark_bl_charges_reviewed(text,uuid) -&gt; jsonb (019; DEFINER; active user): moves calculations/B/L to reviewed and audits; hooks invalidate lines, B/Ls and pendencies.</v>
       </c>
       <c r="E65" t="str">
-        <v>Verified</v>
+        <v>Verified (static)</v>
       </c>
       <c r="F65" t="str">
         <v>-</v>
@@ -2541,7 +2541,7 @@
         <v>mark_bl_ready_and_create_invoice(text,bigint,date,text,uuid) -&gt; jsonb (102_mark_ready_and_invoice_atomic.sql; INVOKER; active+admin): marks ready and creates invoice+ledger in one transaction; any failure rolls back both.</v>
       </c>
       <c r="E67" t="str">
-        <v>Verified</v>
+        <v>Verified (static)</v>
       </c>
       <c r="F67" t="str">
         <v>-</v>
@@ -2701,7 +2701,7 @@
         <v>guard_container_bl_without_containers() AFTER I/U on bls (064) creates a synthetic pendency so an empty container B/L cannot stay calculated/ready; ensure_container_bl_charge_status_default() (065) converts NULL charge_status of CNTR B/Ls to not_calculated; populate_charge_calculation_billing_metadata() (025) fills manifest and commercial-rule version on charge_calculations.</v>
       </c>
       <c r="E72" t="str">
-        <v>Verified</v>
+        <v>Verified (static)</v>
       </c>
       <c r="F72" t="str">
         <v>-</v>
@@ -2733,7 +2733,7 @@
         <v>charge_tables, charge_table_items, customer_rate_overrides: all operations admin-only (010+014). charge_calculations: SELECT admin (014), INSERT/UPDATE active (010), DELETE admin. customer_reconciliation_queue guarded via RPCs.</v>
       </c>
       <c r="E73" t="str">
-        <v>Verified</v>
+        <v>Verified (static)</v>
       </c>
       <c r="F73" t="str">
         <v>-</v>
@@ -3149,7 +3149,7 @@
         <v>assign_invoice_number() BEFORE INSERT on invoices (003) fills the annual sequential number; fn_block_invoice_overdue_customer() (031) blocks a new invoice when the customer has an overdue local invoice; prevent_duplicate_active_invoice_bl_link() (064) rejects a second active/paid link for the same B/L.</v>
       </c>
       <c r="E86" t="str">
-        <v>Verified</v>
+        <v>Verified (static)</v>
       </c>
       <c r="F86" t="str">
         <v>-</v>
@@ -3181,7 +3181,7 @@
         <v>pg_cron job mark-overdue-invoices (06:00 UTC; 031) runs mark_overdue_invoices() over local invoices; demurrage was removed from overdue enforcement by 157_demurrage_drop_overdue.sql (demurrage has no due_date/overdue).</v>
       </c>
       <c r="E87" t="str">
-        <v>Verified</v>
+        <v>Verified (static)</v>
       </c>
       <c r="F87" t="str">
         <v>-</v>
@@ -3341,7 +3341,7 @@
         <v>invoices, payments, invoice_bls, billing_batches (SELECT active per 041), bl_receivables and invoice_receivable_links: financial families are admin-only for writes (and mostly for reads) per 010+014+020 and the ledger migrations; operational surfaces read through RPCs.</v>
       </c>
       <c r="E92" t="str">
-        <v>Verified</v>
+        <v>Verified (static)</v>
       </c>
       <c r="F92" t="str">
         <v>-</v>
@@ -3437,7 +3437,7 @@
         <v>src/App.tsx renders Navigate to /demurrage with replace.</v>
       </c>
       <c r="E95" t="str">
-        <v>Verified</v>
+        <v>Verified (static)</v>
       </c>
       <c r="F95" t="str">
         <v>-</v>
@@ -3661,7 +3661,7 @@
         <v>Edge Function recalc-demurrage-ptax: requires Authorization bearer exactly equal to SUPABASE_SERVICE_ROLE_KEY (timing-safe compare); queries BCB CotacaoDolarPeriodo for the last ~10 days, top 1 by dataHoraCotacao desc (never 'today only', so weekends/holidays return the latest quote); passes raw cotacaoVenda to recalculate_demurrage_invoices (markup applied in DB); aborts with error only on HTTP/network failure or empty period; designed to be scheduled weekdays ~14h BRT.</v>
       </c>
       <c r="E102" t="str">
-        <v>Verified</v>
+        <v>Verified (static)</v>
       </c>
       <c r="F102" t="str">
         <v>-</v>
@@ -3853,7 +3853,7 @@
         <v>reconcile_invoice_payment_by_txid(text,numeric,timestamptz) -&gt; jsonb (067; DEFINER; active+admin): strict TXID match; records payment/settlement and updates invoice/receivables.</v>
       </c>
       <c r="E108" t="str">
-        <v>Verified</v>
+        <v>Verified (static)</v>
       </c>
       <c r="F108" t="str">
         <v>-</v>
@@ -3949,7 +3949,7 @@
         <v>src/App.tsx renders Navigate to /reconciliacao with replace.</v>
       </c>
       <c r="E111" t="str">
-        <v>Verified</v>
+        <v>Verified (static)</v>
       </c>
       <c r="F111" t="str">
         <v>-</v>
@@ -4365,7 +4365,7 @@
         <v>trg_notify_invoice_issued (invoices status -&gt; issued), trg_notify_demurrage_issued (demurrage_invoices) and trg_notify_dispute_responded (dispute_status -&gt; resolvido) insert portal_notifications rows (116_portal_fase2_notifications_disputes_profile.sql); this in-app path is the active customer notification mechanism (email is off by decision).</v>
       </c>
       <c r="E124" t="str">
-        <v>Verified</v>
+        <v>Verified (static)</v>
       </c>
       <c r="F124" t="str">
         <v>-</v>
@@ -4429,7 +4429,7 @@
         <v>notify-invoice-issued: bearer must equal SUPABASE_SERVICE_ROLE_KEY (timing-safe); accepts absent Origin or Origin == SUPABASE_URL; service role re-reads invoices/customers/customer_contacts (no DB writes) and sends via Resend; missing recipient/key -&gt; skipped/sent:false; auth failure 401; Resend/parse failure 500. No functions.invoke caller exists in src and no webhook is configured in the repo — inactive by decision; customer notification is in-app via trg_notify_invoice_issued.</v>
       </c>
       <c r="E126" t="str">
-        <v>Verified</v>
+        <v>Verified (static)</v>
       </c>
       <c r="F126" t="str">
         <v>-</v>
@@ -4621,7 +4621,7 @@
         <v>prevent_duplicate_active_invoice_granite_bl_link() BEFORE I/U on invoice_granite_bls (064) rejects a second active/paid link for the same granite B/L.</v>
       </c>
       <c r="E132" t="str">
-        <v>Verified</v>
+        <v>Verified (static)</v>
       </c>
       <c r="F132" t="str">
         <v>-</v>
@@ -4653,7 +4653,7 @@
         <v>granite_manifests, granite_bls, granite_bl_charges, granite_rates (042 final + 050 alignment): active users read/insert/update; admin deletes; invoice_granite_bls follows the financial family.</v>
       </c>
       <c r="E133" t="str">
-        <v>Verified</v>
+        <v>Verified (static)</v>
       </c>
       <c r="F133" t="str">
         <v>-</v>
@@ -4877,7 +4877,7 @@
         <v>customers and customer_contacts (010 final): active users read/insert/update; admin deletes; Portal profile writes go only through portal_update_profile; contact email participates in the review gate.</v>
       </c>
       <c r="E140" t="str">
-        <v>Verified</v>
+        <v>Verified (static)</v>
       </c>
       <c r="F140" t="str">
         <v>-</v>
@@ -4905,7 +4905,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <cols>
     <col min="1" max="1" width="36.83203125" customWidth="1"/>
     <col min="2" max="2" width="60.83203125" customWidth="1"/>
@@ -4945,15 +4945,23 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
+        <v>Status: Verified (static)</v>
+      </c>
+      <c r="B5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
         <v>Status: Verified</v>
       </c>
-      <c r="B5">
-        <v>139</v>
+      <c r="B6">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/spec/2026-07-02-behavioral-spec.xlsx
+++ b/docs/spec/2026-07-02-behavioral-spec.xlsx
@@ -7,7 +7,7 @@
     <sheet name="Summary" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Behavioral Spec'!$A$1:$J$140</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Behavioral Spec'!$A$1:$J$143</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J140"/>
+  <dimension ref="A1:J143"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -1113,7 +1113,7 @@
         <v>Vitest: Viagens.behavior.test.tsx; VoyageSectionCards.test.tsx; voyageTimeline.behavior.test.ts</v>
       </c>
       <c r="I22" t="str">
-        <v>src/pages/Viagens.tsx; src/pages/viagensHelpers.ts; src/services/voyageTimeline.ts</v>
+        <v>src/pages/Viagens.tsx; src/services/voyageSummaries.ts; src/services/voyageTimeline.ts</v>
       </c>
       <c r="J22" t="str">
         <v>-</v>
@@ -4895,10 +4895,106 @@
         <v>Verified by code read — SQL/trigger/cron/edge or live-DB RLS surface with no executable assertion in this environment (static is the strongest method available).</v>
       </c>
     </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>VOY-OMIT-01</v>
+      </c>
+      <c r="B141" t="str">
+        <v>Viagens</v>
+      </c>
+      <c r="C141" t="str">
+        <v>As an operator I omit a port call and keep traceability</v>
+      </c>
+      <c r="D141" t="str">
+        <v>OmitEscalaModal calls omit_voyage_escala; the RPC writes voyage_omissions, audit_logs field omitted=true, default bl_transshipments rows and a transshipment portal notification; omitted PODs are ignored by next-call and completion derivations.</v>
+      </c>
+      <c r="E141" t="str">
+        <v>Verified</v>
+      </c>
+      <c r="F141" t="str">
+        <v>-</v>
+      </c>
+      <c r="G141" t="str">
+        <v>-</v>
+      </c>
+      <c r="H141" t="str">
+        <v>Vitest: voyageOmissionsMigration.test.ts; voyageSummaries.omitted.test.ts; voyageRouteSchedules.omitted.test.ts</v>
+      </c>
+      <c r="I141" t="str">
+        <v>src/components/voyages/OmitEscalaModal.tsx; src/services/transshipments.ts; src/services/voyageSummaries.ts; src/services/voyageRouteSchedules.ts; supabase/migrations/174_voyage_omissions_transshipments.sql</v>
+      </c>
+      <c r="J141" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>VOY-OMIT-02</v>
+      </c>
+      <c r="B142" t="str">
+        <v>Portal</v>
+      </c>
+      <c r="C142" t="str">
+        <v>As a portal customer I do not see omitted PODs in the public schedule</v>
+      </c>
+      <c r="D142" t="str">
+        <v>portal_ship_schedule includes omitted_pods and filters audit_logs field_name='omitted' alongside deleted pods before returning the schedule projection.</v>
+      </c>
+      <c r="E142" t="str">
+        <v>Verified</v>
+      </c>
+      <c r="F142" t="str">
+        <v>-</v>
+      </c>
+      <c r="G142" t="str">
+        <v>-</v>
+      </c>
+      <c r="H142" t="str">
+        <v>Vitest: portalShipScheduleOmitted.test.ts</v>
+      </c>
+      <c r="I142" t="str">
+        <v>supabase/migrations/175_portal_ship_schedule_hide_omitted.sql; src/services/portalScheduleVoyages.ts</v>
+      </c>
+      <c r="J142" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>VOY-COD-01</v>
+      </c>
+      <c r="B143" t="str">
+        <v>Viagens</v>
+      </c>
+      <c r="C143" t="str">
+        <v>As an operator I choose transshipment or COD per B/L</v>
+      </c>
+      <c r="D143" t="str">
+        <v>TransshipmentPanel calls set_bl_transshipment or set_bl_cod; transshipment stores third-party vessel reference, while COD clears those fields and updates bls.pod to the discharge port through audited RPCs.</v>
+      </c>
+      <c r="E143" t="str">
+        <v>Verified</v>
+      </c>
+      <c r="F143" t="str">
+        <v>-</v>
+      </c>
+      <c r="G143" t="str">
+        <v>-</v>
+      </c>
+      <c r="H143" t="str">
+        <v>Vitest: transshipments.test.ts</v>
+      </c>
+      <c r="I143" t="str">
+        <v>src/components/voyages/TransshipmentPanel.tsx; src/hooks/useTransshipments.ts; src/services/transshipments.ts; supabase/migrations/174_voyage_omissions_transshipments.sql</v>
+      </c>
+      <c r="J143" t="str">
+        <v>-</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J140"/>
+  <autoFilter ref="A1:J143"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J140"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J143"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4924,7 +5020,7 @@
         <v>Source CSV</v>
       </c>
       <c r="B2" t="str">
-        <v>docs/spec/2026-07-02-behavioral-spec.csv</v>
+        <v>C:\Users\Lucca\Downloads\transhipping-desk2\docs\spec\2026-07-02-behavioral-spec.csv</v>
       </c>
     </row>
     <row r="3">
@@ -4932,7 +5028,7 @@
         <v>Generated</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-07-02</v>
+        <v>2026-07-09</v>
       </c>
     </row>
     <row r="4">
@@ -4940,7 +5036,7 @@
         <v>Total stories</v>
       </c>
       <c r="B4">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5">
@@ -4956,7 +5052,7 @@
         <v>Status: Verified</v>
       </c>
       <c r="B6">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
